--- a/data_lake/industry/Logistics/Logistic manager index.xlsx
+++ b/data_lake/industry/Logistics/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\Logistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/Logistics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A755FC-ADB6-481D-AB65-4CABFE3F1943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963C7D05-1883-E149-BA81-14773DE3CA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,65 @@
     <sheet name="info" sheetId="2" r:id="rId3"/>
     <sheet name="fig" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">LMI!$B$2:$B$118</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">LMI!$E$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">LMI!$I$2:$I$118</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">LMI!$J$1</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">LMI!$J$2:$J$118</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">LMI!$K$1</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">LMI!$K$2:$K$118</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">LMI!$L$1</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">LMI!$L$2:$L$118</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">LMI!$M$1</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">LMI!$M$2:$M$118</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">LMI!$B$2:$B$118</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">LMI!$E$2:$E$118</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">LMI!$E$1</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">LMI!$E$2:$E$118</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">LMI!$F$1</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">LMI!$F$2:$F$118</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">LMI!$G$1</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">LMI!$G$2:$G$118</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">LMI!$H$1</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">LMI!$H$2:$H$118</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">LMI!$I$1</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">LMI!$I$2:$I$118</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">LMI!$F$1</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">LMI!$J$1</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">LMI!$J$2:$J$118</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">LMI!$K$1</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">LMI!$K$2:$K$118</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">LMI!$L$1</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">LMI!$L$2:$L$118</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">LMI!$M$1</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">LMI!$M$2:$M$118</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">LMI!$B$2:$B$118</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">LMI!$E$1</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">LMI!$F$2:$F$118</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">LMI!$E$2:$E$118</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">LMI!$F$1</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">LMI!$F$2:$F$118</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">LMI!$G$1</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">LMI!$G$2:$G$118</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">LMI!$H$1</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">LMI!$H$2:$H$118</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">LMI!$I$1</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">LMI!$I$2:$I$118</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">LMI!$J$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">LMI!$G$1</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">LMI!$J$2:$J$118</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">LMI!$K$1</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">LMI!$K$2:$K$118</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">LMI!$L$1</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">LMI!$L$2:$L$118</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">LMI!$M$1</definedName>
+    <definedName name="_xlchart.v1.56" hidden="1">LMI!$M$2:$M$118</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">LMI!$G$2:$G$118</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">LMI!$H$1</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">LMI!$H$2:$H$118</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">LMI!$I$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -282,10 +341,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -303,7 +362,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7119,6 +7178,8 @@
         <c:axId val="1834800832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="47118"/>
+          <c:min val="43831"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -7305,7 +7366,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12825,6 +12886,8 @@
         <c:axId val="1872126272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="47118"/>
+          <c:min val="43831"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -14464,16 +14527,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:N119"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="11" customWidth="1"/>
-    <col min="6" max="13" width="11.109375" style="12" customWidth="1"/>
-    <col min="14" max="14" width="21.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="11" customWidth="1"/>
+    <col min="6" max="13" width="11.1640625" style="12" customWidth="1"/>
+    <col min="14" max="14" width="21.5" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -17290,7 +17353,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D67" s="10" t="str">
-        <f t="shared" ref="D67:D118" si="1">IF(
+        <f t="shared" ref="D67:D119" si="1">IF(
 AND(
   B67 &gt;= IF(
          YEAR(B67)&gt;=2007,
@@ -19480,6 +19543,21 @@
       </c>
       <c r="N118" s="12"/>
     </row>
+    <row r="119" spans="1:14">
+      <c r="A119" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B119" s="8">
+        <v>46210</v>
+      </c>
+      <c r="C119" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D119" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19489,16 +19567,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF85ECF-5DA2-D446-A4EF-6579CB12CAA0}">
-  <dimension ref="A1:N94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:N95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="15" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="10.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
@@ -21295,7 +21373,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D43" s="10" t="str">
-        <f t="shared" ref="D43:D94" si="1">IF(
+        <f t="shared" ref="D43:D95" si="1">IF(
 AND(
   B43 &gt;= IF(
          YEAR(B43)&gt;=2007,
@@ -23483,6 +23561,21 @@
         <v>91.4</v>
       </c>
     </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B95" s="8">
+        <v>46210</v>
+      </c>
+      <c r="C95" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D95" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23491,9 +23584,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
@@ -23532,7 +23625,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>

--- a/data_lake/industry/Logistics/Logistic manager index.xlsx
+++ b/data_lake/industry/Logistics/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9514CA17-DAD5-413B-A348-DCF429D5B499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162AFBF4-EB43-4B3D-B4A7-27892F92B7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -698,6 +698,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1454,6 +1457,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2210,6 +2216,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2966,6 +2975,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3722,6 +3734,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4477,6 +4492,9 @@
                 </c:pt>
                 <c:pt idx="117">
                   <c:v>46210</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5236,6 +5254,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5994,6 +6015,9 @@
                 <c:pt idx="117">
                   <c:v>46210</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6751,6 +6775,9 @@
                 </c:pt>
                 <c:pt idx="117">
                   <c:v>46210</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>46238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14490,7 +14517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" style="11" bestFit="1" customWidth="1"/>
@@ -17316,7 +17343,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D67" s="13" t="str">
-        <f t="shared" ref="D67:D119" si="1">IF(
+        <f t="shared" ref="D67:D120" si="1">IF(
 AND(
   B67 &gt;= IF(
          YEAR(B67)&gt;=2007,
@@ -19548,6 +19575,21 @@
         <v>92.4</v>
       </c>
     </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A120" s="11">
+        <v>46204</v>
+      </c>
+      <c r="B120" s="11">
+        <v>46238</v>
+      </c>
+      <c r="C120" s="12">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D120" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19557,7 +19599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF85ECF-5DA2-D446-A4EF-6579CB12CAA0}">
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" style="11" bestFit="1" customWidth="1"/>
@@ -21360,7 +21402,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D43" s="13" t="str">
-        <f t="shared" ref="D43:D95" si="1">IF(
+        <f t="shared" ref="D43:D96" si="1">IF(
 AND(
   B43 &gt;= IF(
          YEAR(B43)&gt;=2007,
@@ -23588,6 +23630,21 @@
       </c>
       <c r="M95" s="18">
         <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="11">
+        <v>46204</v>
+      </c>
+      <c r="B96" s="11">
+        <v>46238</v>
+      </c>
+      <c r="C96" s="12">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D96" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/Logistics/Logistic manager index.xlsx
+++ b/data_lake/industry/Logistics/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\Logistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/Logistics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE79F90-58BF-491A-92EB-58649A62EA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE6B978-2214-3F40-9D9A-D0CF5249E4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18000" yWindow="780" windowWidth="18000" windowHeight="20760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -280,32 +280,32 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -320,7 +320,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -328,7 +328,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -372,11 +372,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -388,52 +388,52 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -451,7 +451,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7563,7 +7563,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14833,20 +14833,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.09765625" style="13" customWidth="1"/>
-    <col min="6" max="13" width="9.09765625" style="14" customWidth="1"/>
-    <col min="14" max="15" width="9.09765625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="13" customWidth="1"/>
+    <col min="6" max="13" width="9.1640625" style="14" customWidth="1"/>
+    <col min="14" max="15" width="9.1640625" style="16" customWidth="1"/>
     <col min="16" max="31" width="9" style="16"/>
     <col min="32" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -14941,7 +14941,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31">
       <c r="A2" s="10">
         <v>42614</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>65.599999999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31">
       <c r="A3" s="10">
         <v>42644</v>
       </c>
@@ -15055,7 +15055,7 @@
         <v>65.099999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31">
       <c r="A4" s="10">
         <v>42675</v>
       </c>
@@ -15097,7 +15097,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31">
       <c r="A5" s="10">
         <v>42705</v>
       </c>
@@ -15139,7 +15139,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31">
       <c r="A6" s="10">
         <v>42736</v>
       </c>
@@ -15181,7 +15181,7 @@
         <v>75.3</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31">
       <c r="A7" s="10">
         <v>42767</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>75.3</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31">
       <c r="A8" s="10">
         <v>42795</v>
       </c>
@@ -15265,7 +15265,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31">
       <c r="A9" s="10">
         <v>42826</v>
       </c>
@@ -15307,7 +15307,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31">
       <c r="A10" s="10">
         <v>42856</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31">
       <c r="A11" s="10">
         <v>42887</v>
       </c>
@@ -15391,7 +15391,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31">
       <c r="A12" s="10">
         <v>42917</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>76.12</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31">
       <c r="A13" s="10">
         <v>42948</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>76.12</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31">
       <c r="A14" s="10">
         <v>42979</v>
       </c>
@@ -15517,7 +15517,7 @@
         <v>86.03</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31">
       <c r="A15" s="10">
         <v>43009</v>
       </c>
@@ -15559,7 +15559,7 @@
         <v>86.03</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31">
       <c r="A16" s="10">
         <v>43040</v>
       </c>
@@ -15601,7 +15601,7 @@
         <v>86.03</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="10">
         <v>43070</v>
       </c>
@@ -15643,7 +15643,7 @@
         <v>86.03</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="10">
         <v>43101</v>
       </c>
@@ -15685,7 +15685,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="10">
         <v>43132</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="10">
         <v>43160</v>
       </c>
@@ -15769,7 +15769,7 @@
         <v>95.81</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="10">
         <v>43191</v>
       </c>
@@ -15811,7 +15811,7 @@
         <v>95.81</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="10">
         <v>43221</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>94.05</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="10">
         <v>43252</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>94.05</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="10">
         <v>43282</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>92.68</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="10">
         <v>43313</v>
       </c>
@@ -15979,7 +15979,7 @@
         <v>92.68</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="10">
         <v>43344</v>
       </c>
@@ -16021,7 +16021,7 @@
         <v>89.9</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="10">
         <v>43374</v>
       </c>
@@ -16063,7 +16063,7 @@
         <v>87.94</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="10">
         <v>43405</v>
       </c>
@@ -16105,7 +16105,7 @@
         <v>79.790000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="10">
         <v>43435</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>74.34</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="10">
         <v>43466</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>69.38</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="10">
         <v>43497</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>67.23</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="10">
         <v>43525</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13">
       <c r="A33" s="10">
         <v>43556</v>
       </c>
@@ -16315,7 +16315,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13">
       <c r="A34" s="10">
         <v>43586</v>
       </c>
@@ -16357,7 +16357,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13">
       <c r="A35" s="10">
         <v>43617</v>
       </c>
@@ -16399,7 +16399,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13">
       <c r="A36" s="10">
         <v>43647</v>
       </c>
@@ -16441,7 +16441,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13">
       <c r="A37" s="10">
         <v>43678</v>
       </c>
@@ -16483,7 +16483,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13">
       <c r="A38" s="10">
         <v>43709</v>
       </c>
@@ -16525,7 +16525,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13">
       <c r="A39" s="10">
         <v>43739</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13">
       <c r="A40" s="10">
         <v>43770</v>
       </c>
@@ -16609,7 +16609,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13">
       <c r="A41" s="10">
         <v>43800</v>
       </c>
@@ -16651,7 +16651,7 @@
         <v>52.74</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13">
       <c r="A42" s="10">
         <v>43831</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13">
       <c r="A43" s="10">
         <v>43862</v>
       </c>
@@ -16735,7 +16735,7 @@
         <v>48.98</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13">
       <c r="A44" s="10">
         <v>43891</v>
       </c>
@@ -16777,7 +16777,7 @@
         <v>65.52</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13">
       <c r="A45" s="10">
         <v>43922</v>
       </c>
@@ -16819,7 +16819,7 @@
         <v>37.659999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13">
       <c r="A46" s="10">
         <v>43952</v>
       </c>
@@ -16861,7 +16861,7 @@
         <v>49.07</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13">
       <c r="A47" s="10">
         <v>43983</v>
       </c>
@@ -16903,7 +16903,7 @@
         <v>64.47</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13">
       <c r="A48" s="10">
         <v>44013</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>72.64</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13">
       <c r="A49" s="10">
         <v>44044</v>
       </c>
@@ -16987,7 +16987,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -17029,7 +17029,7 @@
         <v>87.85</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13">
       <c r="A51" s="10">
         <v>44105</v>
       </c>
@@ -17071,7 +17071,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13">
       <c r="A52" s="10">
         <v>44136</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>85.8</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13">
       <c r="A53" s="10">
         <v>44166</v>
       </c>
@@ -17155,7 +17155,7 @@
         <v>85.1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13">
       <c r="A54" s="10">
         <v>44197</v>
       </c>
@@ -17197,7 +17197,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13">
       <c r="A55" s="10">
         <v>44228</v>
       </c>
@@ -17239,7 +17239,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13">
       <c r="A56" s="10">
         <v>44256</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13">
       <c r="A57" s="10">
         <v>44287</v>
       </c>
@@ -17323,7 +17323,7 @@
         <v>92.6</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13">
       <c r="A58" s="10">
         <v>44317</v>
       </c>
@@ -17365,7 +17365,7 @@
         <v>91.2</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13">
       <c r="A59" s="10">
         <v>44348</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>87.3</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13">
       <c r="A60" s="10">
         <v>44378</v>
       </c>
@@ -17449,7 +17449,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13">
       <c r="A61" s="10">
         <v>44409</v>
       </c>
@@ -17491,7 +17491,7 @@
         <v>93.7</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13">
       <c r="A62" s="10">
         <v>44440</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>92.4</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13">
       <c r="A63" s="10">
         <v>44470</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>90.7</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13">
       <c r="A64" s="10">
         <v>44501</v>
       </c>
@@ -17617,7 +17617,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13">
       <c r="A65" s="10">
         <v>44531</v>
       </c>
@@ -17659,7 +17659,7 @@
         <v>87.6</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13">
       <c r="A66" s="10">
         <v>44562</v>
       </c>
@@ -17701,7 +17701,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13">
       <c r="A67" s="10">
         <v>44593</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13">
       <c r="A68" s="10">
         <v>44621</v>
       </c>
@@ -17800,7 +17800,7 @@
         <v>89.7</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13">
       <c r="A69" s="10">
         <v>44652</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13">
       <c r="A70" s="10">
         <v>44682</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13">
       <c r="A71" s="10">
         <v>44713</v>
       </c>
@@ -17926,7 +17926,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13">
       <c r="A72" s="10">
         <v>44743</v>
       </c>
@@ -17968,7 +17968,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13">
       <c r="A73" s="10">
         <v>44774</v>
       </c>
@@ -18010,7 +18010,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13">
       <c r="A74" s="10">
         <v>44805</v>
       </c>
@@ -18052,7 +18052,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13">
       <c r="A75" s="10">
         <v>44835</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13">
       <c r="A76" s="10">
         <v>44866</v>
       </c>
@@ -18136,7 +18136,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13">
       <c r="A77" s="10">
         <v>44896</v>
       </c>
@@ -18178,7 +18178,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13">
       <c r="A78" s="10">
         <v>44927</v>
       </c>
@@ -18220,7 +18220,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13">
       <c r="A79" s="10">
         <v>44958</v>
       </c>
@@ -18262,7 +18262,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13">
       <c r="A80" s="10">
         <v>44986</v>
       </c>
@@ -18304,7 +18304,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13">
       <c r="A81" s="10">
         <v>45017</v>
       </c>
@@ -18346,7 +18346,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13">
       <c r="A82" s="10">
         <v>45047</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13">
       <c r="A83" s="10">
         <v>45078</v>
       </c>
@@ -18430,7 +18430,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13">
       <c r="A84" s="10">
         <v>45108</v>
       </c>
@@ -18472,7 +18472,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13">
       <c r="A85" s="10">
         <v>45139</v>
       </c>
@@ -18514,7 +18514,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13">
       <c r="A86" s="10">
         <v>45170</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13">
       <c r="A87" s="10">
         <v>45200</v>
       </c>
@@ -18598,7 +18598,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13">
       <c r="A88" s="10">
         <v>45231</v>
       </c>
@@ -18640,7 +18640,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13">
       <c r="A89" s="10">
         <v>45261</v>
       </c>
@@ -18682,7 +18682,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13">
       <c r="A90" s="10">
         <v>45292</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13">
       <c r="A91" s="10">
         <v>45323</v>
       </c>
@@ -18766,7 +18766,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13">
       <c r="A92" s="10">
         <v>45352</v>
       </c>
@@ -18808,7 +18808,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13">
       <c r="A93" s="10">
         <v>45383</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>44.1</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13">
       <c r="A94" s="10">
         <v>45413</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13">
       <c r="A95" s="10">
         <v>45444</v>
       </c>
@@ -18934,7 +18934,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13">
       <c r="A96" s="10">
         <v>45474</v>
       </c>
@@ -18976,7 +18976,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31">
       <c r="A97" s="10">
         <v>45505</v>
       </c>
@@ -19018,7 +19018,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31">
       <c r="A98" s="10">
         <v>45536</v>
       </c>
@@ -19060,7 +19060,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31">
       <c r="A99" s="10">
         <v>45566</v>
       </c>
@@ -19102,7 +19102,7 @@
         <v>64.099999999999994</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31">
       <c r="A100" s="10">
         <v>45597</v>
       </c>
@@ -19144,7 +19144,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31">
       <c r="A101" s="10">
         <v>45627</v>
       </c>
@@ -19186,7 +19186,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31">
       <c r="A102" s="10">
         <v>45658</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31">
       <c r="A103" s="10">
         <v>45689</v>
       </c>
@@ -19270,7 +19270,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31">
       <c r="A104" s="10">
         <v>45717</v>
       </c>
@@ -19312,7 +19312,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31">
       <c r="A105" s="10">
         <v>45748</v>
       </c>
@@ -19354,7 +19354,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31">
       <c r="A106" s="10">
         <v>45778</v>
       </c>
@@ -19396,7 +19396,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31">
       <c r="A107" s="10">
         <v>45809</v>
       </c>
@@ -19438,7 +19438,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31">
       <c r="A108" s="10">
         <v>45839</v>
       </c>
@@ -19534,7 +19534,7 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31">
       <c r="A109" s="10">
         <v>45870</v>
       </c>
@@ -19575,8 +19575,62 @@
       <c r="M109" s="13">
         <v>65.099999999999994</v>
       </c>
+      <c r="N109" s="16">
+        <v>60.1</v>
+      </c>
+      <c r="O109" s="16">
+        <v>62.7</v>
+      </c>
+      <c r="P109" s="16">
+        <v>51.5</v>
+      </c>
+      <c r="Q109" s="16">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="R109" s="16">
+        <v>55.3</v>
+      </c>
+      <c r="S109" s="16">
+        <v>51.8</v>
+      </c>
+      <c r="T109" s="16">
+        <v>57.6</v>
+      </c>
+      <c r="U109" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="V109" s="16">
+        <v>71</v>
+      </c>
+      <c r="W109" s="16">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="X109" s="16">
+        <v>62.7</v>
+      </c>
+      <c r="Y109" s="16">
+        <v>59.3</v>
+      </c>
+      <c r="Z109" s="16">
+        <v>49.2</v>
+      </c>
+      <c r="AA109" s="16">
+        <v>51.9</v>
+      </c>
+      <c r="AB109" s="16">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="AC109" s="16">
+        <v>81.5</v>
+      </c>
+      <c r="AD109" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="AE109" s="16">
+        <v>57.1</v>
+      </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31">
       <c r="A110" s="10">
         <v>45901</v>
       </c>
@@ -19617,8 +19671,62 @@
       <c r="M110" s="13">
         <v>54.2</v>
       </c>
+      <c r="N110" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="O110" s="16">
+        <v>60.1</v>
+      </c>
+      <c r="P110" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="Q110" s="16">
+        <v>61.1</v>
+      </c>
+      <c r="R110" s="16">
+        <v>50</v>
+      </c>
+      <c r="S110" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="T110" s="16">
+        <v>56.5</v>
+      </c>
+      <c r="U110" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="V110" s="16">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="W110" s="16">
+        <v>67.7</v>
+      </c>
+      <c r="X110" s="16">
+        <v>65.3</v>
+      </c>
+      <c r="Y110" s="16">
+        <v>65.3</v>
+      </c>
+      <c r="Z110" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="AA110" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="AB110" s="16">
+        <v>73.3</v>
+      </c>
+      <c r="AC110" s="16">
+        <v>79.2</v>
+      </c>
+      <c r="AD110" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="AE110" s="16">
+        <v>54.2</v>
+      </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31">
       <c r="A111" s="10">
         <v>45931</v>
       </c>
@@ -19659,8 +19767,62 @@
       <c r="M111" s="13">
         <v>61.7</v>
       </c>
+      <c r="N111" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="O111" s="16">
+        <v>58.3</v>
+      </c>
+      <c r="P111" s="16">
+        <v>56.4</v>
+      </c>
+      <c r="Q111" s="16">
+        <v>70</v>
+      </c>
+      <c r="R111" s="16">
+        <v>55.8</v>
+      </c>
+      <c r="S111" s="16">
+        <v>60</v>
+      </c>
+      <c r="T111" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="U111" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="V111" s="16">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="W111" s="16">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="X111" s="16">
+        <v>58.5</v>
+      </c>
+      <c r="Y111" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="Z111" s="16">
+        <v>48.3</v>
+      </c>
+      <c r="AA111" s="16">
+        <v>57.7</v>
+      </c>
+      <c r="AB111" s="16">
+        <v>75</v>
+      </c>
+      <c r="AC111" s="16">
+        <v>70</v>
+      </c>
+      <c r="AD111" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="AE111" s="16">
+        <v>47.6</v>
+      </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31">
       <c r="A112" s="10">
         <v>45962</v>
       </c>
@@ -19701,8 +19863,62 @@
       <c r="M112" s="13">
         <v>64.900000000000006</v>
       </c>
+      <c r="N112" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="O112" s="16">
+        <v>59.1</v>
+      </c>
+      <c r="P112" s="16">
+        <v>63</v>
+      </c>
+      <c r="Q112" s="16">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="R112" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="S112" s="16">
+        <v>44.1</v>
+      </c>
+      <c r="T112" s="16">
+        <v>49</v>
+      </c>
+      <c r="U112" s="16">
+        <v>52.8</v>
+      </c>
+      <c r="V112" s="16">
+        <v>61.4</v>
+      </c>
+      <c r="W112" s="16">
+        <v>66.7</v>
+      </c>
+      <c r="X112" s="16">
+        <v>44.2</v>
+      </c>
+      <c r="Y112" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="Z112" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="AA112" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="AB112" s="16">
+        <v>68.3</v>
+      </c>
+      <c r="AC112" s="16">
+        <v>76.3</v>
+      </c>
+      <c r="AD112" s="16">
+        <v>46.3</v>
+      </c>
+      <c r="AE112" s="16">
+        <v>65.8</v>
+      </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31">
       <c r="A113" s="10">
         <v>45992</v>
       </c>
@@ -19743,8 +19959,62 @@
       <c r="M113" s="14">
         <v>66.7</v>
       </c>
+      <c r="N113" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="O113" s="16">
+        <v>47.2</v>
+      </c>
+      <c r="P113" s="16">
+        <v>69.5</v>
+      </c>
+      <c r="Q113" s="16">
+        <v>59.1</v>
+      </c>
+      <c r="R113" s="16">
+        <v>62.1</v>
+      </c>
+      <c r="S113" s="16">
+        <v>47.6</v>
+      </c>
+      <c r="T113" s="16">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="U113" s="16">
+        <v>42.9</v>
+      </c>
+      <c r="V113" s="16">
+        <v>68.8</v>
+      </c>
+      <c r="W113" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="X113" s="16">
+        <v>44.6</v>
+      </c>
+      <c r="Y113" s="16">
+        <v>38.1</v>
+      </c>
+      <c r="Z113" s="16">
+        <v>59.8</v>
+      </c>
+      <c r="AA113" s="16">
+        <v>65</v>
+      </c>
+      <c r="AB113" s="16">
+        <v>63.5</v>
+      </c>
+      <c r="AC113" s="16">
+        <v>61.4</v>
+      </c>
+      <c r="AD113" s="16">
+        <v>35.6</v>
+      </c>
+      <c r="AE113" s="16">
+        <v>34.1</v>
+      </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31">
       <c r="A114" s="10">
         <v>46023</v>
       </c>
@@ -19785,8 +20055,62 @@
       <c r="M114" s="14">
         <v>71.400000000000006</v>
       </c>
+      <c r="N114" s="16">
+        <v>59.7</v>
+      </c>
+      <c r="O114" s="16">
+        <v>58.3</v>
+      </c>
+      <c r="P114" s="16">
+        <v>71.8</v>
+      </c>
+      <c r="Q114" s="16">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="R114" s="16">
+        <v>60.2</v>
+      </c>
+      <c r="S114" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="T114" s="16">
+        <v>45.9</v>
+      </c>
+      <c r="U114" s="16">
+        <v>50</v>
+      </c>
+      <c r="V114" s="16">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="W114" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="X114" s="16">
+        <v>55.1</v>
+      </c>
+      <c r="Y114" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="Z114" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="AA114" s="16">
+        <v>47.1</v>
+      </c>
+      <c r="AB114" s="16">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="AC114" s="16">
+        <v>73.5</v>
+      </c>
+      <c r="AD114" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="AE114" s="16">
+        <v>54.4</v>
+      </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31">
       <c r="A115" s="10">
         <v>46054</v>
       </c>
@@ -19827,8 +20151,62 @@
       <c r="M115" s="14">
         <v>76.7</v>
       </c>
+      <c r="N115" s="16">
+        <v>56.2</v>
+      </c>
+      <c r="O115" s="16">
+        <v>59.2</v>
+      </c>
+      <c r="P115" s="16">
+        <v>79.7</v>
+      </c>
+      <c r="Q115" s="16">
+        <v>68.3</v>
+      </c>
+      <c r="R115" s="16">
+        <v>61.5</v>
+      </c>
+      <c r="S115" s="16">
+        <v>62.9</v>
+      </c>
+      <c r="T115" s="16">
+        <v>42</v>
+      </c>
+      <c r="U115" s="16">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="V115" s="16">
+        <v>59.8</v>
+      </c>
+      <c r="W115" s="16">
+        <v>67.2</v>
+      </c>
+      <c r="X115" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="Y115" s="16">
+        <v>65</v>
+      </c>
+      <c r="Z115" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="AA115" s="16">
+        <v>48.3</v>
+      </c>
+      <c r="AB115" s="16">
+        <v>65.2</v>
+      </c>
+      <c r="AC115" s="16">
+        <v>73.3</v>
+      </c>
+      <c r="AD115" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="AE115" s="16">
+        <v>51.7</v>
+      </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31">
       <c r="A116" s="10">
         <v>46082</v>
       </c>
@@ -19869,8 +20247,62 @@
       <c r="M116" s="14">
         <v>89.4</v>
       </c>
+      <c r="N116" s="16">
+        <v>63.6</v>
+      </c>
+      <c r="O116" s="16">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="P116" s="16">
+        <v>89.9</v>
+      </c>
+      <c r="Q116" s="16">
+        <v>89.6</v>
+      </c>
+      <c r="R116" s="16">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="S116" s="16">
+        <v>52.1</v>
+      </c>
+      <c r="T116" s="16">
+        <v>39</v>
+      </c>
+      <c r="U116" s="16">
+        <v>39.6</v>
+      </c>
+      <c r="V116" s="16">
+        <v>67.5</v>
+      </c>
+      <c r="W116" s="16">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="X116" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="Y116" s="16">
+        <v>60.4</v>
+      </c>
+      <c r="Z116" s="16">
+        <v>46.8</v>
+      </c>
+      <c r="AA116" s="16">
+        <v>43.8</v>
+      </c>
+      <c r="AB116" s="16">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="AC116" s="16">
+        <v>87.5</v>
+      </c>
+      <c r="AD116" s="16">
+        <v>51.7</v>
+      </c>
+      <c r="AE116" s="16">
+        <v>62.5</v>
+      </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31">
       <c r="A117" s="10">
         <v>46113</v>
       </c>
@@ -19911,9 +20343,62 @@
       <c r="M117" s="14">
         <v>95</v>
       </c>
-      <c r="N117" s="15"/>
+      <c r="N117" s="16">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="O117" s="16">
+        <v>62.3</v>
+      </c>
+      <c r="P117" s="16">
+        <v>94.2</v>
+      </c>
+      <c r="Q117" s="16">
+        <v>96.8</v>
+      </c>
+      <c r="R117" s="16">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="S117" s="16">
+        <v>55</v>
+      </c>
+      <c r="T117" s="16">
+        <v>26.9</v>
+      </c>
+      <c r="U117" s="16">
+        <v>31.7</v>
+      </c>
+      <c r="V117" s="16">
+        <v>73.3</v>
+      </c>
+      <c r="W117" s="16">
+        <v>71.7</v>
+      </c>
+      <c r="X117" s="16">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="Y117" s="16">
+        <v>56.9</v>
+      </c>
+      <c r="Z117" s="16">
+        <v>44.9</v>
+      </c>
+      <c r="AA117" s="16">
+        <v>46.7</v>
+      </c>
+      <c r="AB117" s="16">
+        <v>75.5</v>
+      </c>
+      <c r="AC117" s="16">
+        <v>73.3</v>
+      </c>
+      <c r="AD117" s="16">
+        <v>57.9</v>
+      </c>
+      <c r="AE117" s="16">
+        <v>53.3</v>
+      </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31">
       <c r="A118" s="10">
         <v>46143</v>
       </c>
@@ -19954,9 +20439,62 @@
       <c r="M118" s="14">
         <v>96</v>
       </c>
-      <c r="N118" s="15"/>
+      <c r="N118" s="15">
+        <v>65.8</v>
+      </c>
+      <c r="O118" s="16">
+        <v>63.8</v>
+      </c>
+      <c r="P118" s="16">
+        <v>96.3</v>
+      </c>
+      <c r="Q118" s="16">
+        <v>95.3</v>
+      </c>
+      <c r="R118" s="16">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="S118" s="16">
+        <v>60.9</v>
+      </c>
+      <c r="T118" s="16">
+        <v>25.7</v>
+      </c>
+      <c r="U118" s="16">
+        <v>45.3</v>
+      </c>
+      <c r="V118" s="16">
+        <v>71</v>
+      </c>
+      <c r="W118" s="16">
+        <v>68.3</v>
+      </c>
+      <c r="X118" s="16">
+        <v>64.2</v>
+      </c>
+      <c r="Y118" s="16">
+        <v>62.5</v>
+      </c>
+      <c r="Z118" s="16">
+        <v>44.3</v>
+      </c>
+      <c r="AA118" s="16">
+        <v>60.9</v>
+      </c>
+      <c r="AB118" s="16">
+        <v>85.3</v>
+      </c>
+      <c r="AC118" s="16">
+        <v>81.3</v>
+      </c>
+      <c r="AD118" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="AE118" s="16">
+        <v>57.8</v>
+      </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31">
       <c r="A119" s="10">
         <v>46174</v>
       </c>
@@ -19997,8 +20535,62 @@
       <c r="M119" s="14">
         <v>92.4</v>
       </c>
+      <c r="N119" s="16">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="O119" s="16">
+        <v>68.5</v>
+      </c>
+      <c r="P119" s="16">
+        <v>90.4</v>
+      </c>
+      <c r="Q119" s="16">
+        <v>97.9</v>
+      </c>
+      <c r="R119" s="16">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="S119" s="16">
+        <v>75</v>
+      </c>
+      <c r="T119" s="16">
+        <v>29.9</v>
+      </c>
+      <c r="U119" s="16">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="V119" s="16">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="W119" s="16">
+        <v>78</v>
+      </c>
+      <c r="X119" s="16">
+        <v>72.7</v>
+      </c>
+      <c r="Y119" s="16">
+        <v>62</v>
+      </c>
+      <c r="Z119" s="16">
+        <v>46.4</v>
+      </c>
+      <c r="AA119" s="16">
+        <v>50</v>
+      </c>
+      <c r="AB119" s="16">
+        <v>72.2</v>
+      </c>
+      <c r="AC119" s="16">
+        <v>84</v>
+      </c>
+      <c r="AD119" s="16">
+        <v>59.1</v>
+      </c>
+      <c r="AE119" s="16">
+        <v>66</v>
+      </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31">
       <c r="A120" s="10">
         <v>46204</v>
       </c>
@@ -20104,19 +20696,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF85ECF-5DA2-D446-A4EF-6579CB12CAA0}">
   <dimension ref="A1:AE96"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="15" customWidth="1"/>
     <col min="6" max="14" width="9" style="16" customWidth="1"/>
     <col min="15" max="31" width="9" style="16"/>
     <col min="32" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" s="17" customFormat="1">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -20211,7 +20803,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31">
       <c r="A2" s="10">
         <v>43344</v>
       </c>
@@ -20268,7 +20860,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31">
       <c r="A3" s="10">
         <v>43374</v>
       </c>
@@ -20310,7 +20902,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31">
       <c r="A4" s="10">
         <v>43405</v>
       </c>
@@ -20352,7 +20944,7 @@
         <v>82.3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31">
       <c r="A5" s="10">
         <v>43435</v>
       </c>
@@ -20394,7 +20986,7 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31">
       <c r="A6" s="10">
         <v>43466</v>
       </c>
@@ -20436,7 +21028,7 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31">
       <c r="A7" s="10">
         <v>43497</v>
       </c>
@@ -20478,7 +21070,7 @@
         <v>74.8</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31">
       <c r="A8" s="10">
         <v>43525</v>
       </c>
@@ -20520,7 +21112,7 @@
         <v>72.2</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31">
       <c r="A9" s="10">
         <v>43556</v>
       </c>
@@ -20562,7 +21154,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31">
       <c r="A10" s="10">
         <v>43586</v>
       </c>
@@ -20604,7 +21196,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31">
       <c r="A11" s="10">
         <v>43617</v>
       </c>
@@ -20646,7 +21238,7 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31">
       <c r="A12" s="10">
         <v>43647</v>
       </c>
@@ -20688,7 +21280,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31">
       <c r="A13" s="10">
         <v>43678</v>
       </c>
@@ -20730,7 +21322,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31">
       <c r="A14" s="10">
         <v>43709</v>
       </c>
@@ -20772,7 +21364,7 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31">
       <c r="A15" s="10">
         <v>43739</v>
       </c>
@@ -20814,7 +21406,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31">
       <c r="A16" s="10">
         <v>43770</v>
       </c>
@@ -20856,7 +21448,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="10">
         <v>43800</v>
       </c>
@@ -20898,7 +21490,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="10">
         <v>43831</v>
       </c>
@@ -20940,7 +21532,7 @@
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="10">
         <v>43862</v>
       </c>
@@ -20982,7 +21574,7 @@
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="10">
         <v>43891</v>
       </c>
@@ -21024,7 +21616,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="10">
         <v>43922</v>
       </c>
@@ -21066,7 +21658,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="10">
         <v>43952</v>
       </c>
@@ -21108,7 +21700,7 @@
         <v>66.400000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="10">
         <v>43983</v>
       </c>
@@ -21150,7 +21742,7 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="10">
         <v>44013</v>
       </c>
@@ -21192,7 +21784,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="10">
         <v>44044</v>
       </c>
@@ -21234,7 +21826,7 @@
         <v>84.1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="10">
         <v>44075</v>
       </c>
@@ -21276,7 +21868,7 @@
         <v>85.8</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="10">
         <v>44105</v>
       </c>
@@ -21318,7 +21910,7 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="10">
         <v>44136</v>
       </c>
@@ -21360,7 +21952,7 @@
         <v>77.900000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="10">
         <v>44166</v>
       </c>
@@ -21402,7 +21994,7 @@
         <v>77.599999999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="10">
         <v>44197</v>
       </c>
@@ -21444,7 +22036,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="10">
         <v>44228</v>
       </c>
@@ -21486,7 +22078,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="10">
         <v>44256</v>
       </c>
@@ -21528,7 +22120,7 @@
         <v>82.1</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13">
       <c r="A33" s="10">
         <v>44287</v>
       </c>
@@ -21570,7 +22162,7 @@
         <v>86.2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13">
       <c r="A34" s="10">
         <v>44317</v>
       </c>
@@ -21612,7 +22204,7 @@
         <v>87.2</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13">
       <c r="A35" s="10">
         <v>44348</v>
       </c>
@@ -21654,7 +22246,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13">
       <c r="A36" s="10">
         <v>44378</v>
       </c>
@@ -21696,7 +22288,7 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13">
       <c r="A37" s="10">
         <v>44409</v>
       </c>
@@ -21738,7 +22330,7 @@
         <v>87.4</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -21780,7 +22372,7 @@
         <v>86.9</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13">
       <c r="A39" s="10">
         <v>44470</v>
       </c>
@@ -21822,7 +22414,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13">
       <c r="A40" s="10">
         <v>44501</v>
       </c>
@@ -21864,7 +22456,7 @@
         <v>84.3</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13">
       <c r="A41" s="10">
         <v>44531</v>
       </c>
@@ -21906,7 +22498,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13">
       <c r="A42" s="10">
         <v>44562</v>
       </c>
@@ -21948,7 +22540,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13">
       <c r="A43" s="10">
         <v>44593</v>
       </c>
@@ -22005,7 +22597,7 @@
         <v>81.8</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13">
       <c r="A44" s="10">
         <v>44621</v>
       </c>
@@ -22047,7 +22639,7 @@
         <v>78.599999999999994</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13">
       <c r="A45" s="10">
         <v>44652</v>
       </c>
@@ -22089,7 +22681,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13">
       <c r="A46" s="10">
         <v>44682</v>
       </c>
@@ -22131,7 +22723,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13">
       <c r="A47" s="10">
         <v>44713</v>
       </c>
@@ -22173,7 +22765,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13">
       <c r="A48" s="10">
         <v>44743</v>
       </c>
@@ -22215,7 +22807,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13">
       <c r="A49" s="10">
         <v>44774</v>
       </c>
@@ -22257,7 +22849,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13">
       <c r="A50" s="10">
         <v>44805</v>
       </c>
@@ -22299,7 +22891,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13">
       <c r="A51" s="10">
         <v>44835</v>
       </c>
@@ -22341,7 +22933,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13">
       <c r="A52" s="10">
         <v>44866</v>
       </c>
@@ -22383,7 +22975,7 @@
         <v>42.1</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13">
       <c r="A53" s="10">
         <v>44896</v>
       </c>
@@ -22425,7 +23017,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13">
       <c r="A54" s="10">
         <v>44927</v>
       </c>
@@ -22467,7 +23059,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13">
       <c r="A55" s="10">
         <v>44958</v>
       </c>
@@ -22509,7 +23101,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13">
       <c r="A56" s="10">
         <v>44986</v>
       </c>
@@ -22551,7 +23143,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13">
       <c r="A57" s="10">
         <v>45017</v>
       </c>
@@ -22593,7 +23185,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13">
       <c r="A58" s="10">
         <v>45047</v>
       </c>
@@ -22635,7 +23227,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13">
       <c r="A59" s="10">
         <v>45078</v>
       </c>
@@ -22677,7 +23269,7 @@
         <v>59.1</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13">
       <c r="A60" s="10">
         <v>45108</v>
       </c>
@@ -22719,7 +23311,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13">
       <c r="A61" s="10">
         <v>45139</v>
       </c>
@@ -22761,7 +23353,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13">
       <c r="A62" s="10">
         <v>45170</v>
       </c>
@@ -22803,7 +23395,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13">
       <c r="A63" s="10">
         <v>45200</v>
       </c>
@@ -22845,7 +23437,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13">
       <c r="A64" s="10">
         <v>45231</v>
       </c>
@@ -22887,7 +23479,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13">
       <c r="A65" s="10">
         <v>45261</v>
       </c>
@@ -22929,7 +23521,7 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13">
       <c r="A66" s="10">
         <v>45292</v>
       </c>
@@ -22971,7 +23563,7 @@
         <v>73.7</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13">
       <c r="A67" s="10">
         <v>45323</v>
       </c>
@@ -23013,7 +23605,7 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13">
       <c r="A68" s="10">
         <v>45352</v>
       </c>
@@ -23055,7 +23647,7 @@
         <v>75.3</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13">
       <c r="A69" s="10">
         <v>45383</v>
       </c>
@@ -23097,7 +23689,7 @@
         <v>73.8</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13">
       <c r="A70" s="10">
         <v>45413</v>
       </c>
@@ -23139,7 +23731,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13">
       <c r="A71" s="10">
         <v>45444</v>
       </c>
@@ -23181,7 +23773,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13">
       <c r="A72" s="10">
         <v>45474</v>
       </c>
@@ -23223,7 +23815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13">
       <c r="A73" s="10">
         <v>45505</v>
       </c>
@@ -23265,7 +23857,7 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13">
       <c r="A74" s="10">
         <v>45536</v>
       </c>
@@ -23307,7 +23899,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13">
       <c r="A75" s="10">
         <v>45566</v>
       </c>
@@ -23349,7 +23941,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13">
       <c r="A76" s="10">
         <v>45597</v>
       </c>
@@ -23391,7 +23983,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13">
       <c r="A77" s="10">
         <v>45627</v>
       </c>
@@ -23433,7 +24025,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13">
       <c r="A78" s="10">
         <v>45658</v>
       </c>
@@ -23475,7 +24067,7 @@
         <v>81.099999999999994</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13">
       <c r="A79" s="10">
         <v>45689</v>
       </c>
@@ -23517,7 +24109,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13">
       <c r="A80" s="10">
         <v>45717</v>
       </c>
@@ -23559,7 +24151,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31">
       <c r="A81" s="10">
         <v>45748</v>
       </c>
@@ -23601,7 +24193,7 @@
         <v>72.3</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31">
       <c r="A82" s="10">
         <v>45778</v>
       </c>
@@ -23643,7 +24235,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31">
       <c r="A83" s="10">
         <v>45809</v>
       </c>
@@ -23685,7 +24277,7 @@
         <v>73.3</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31">
       <c r="A84" s="10">
         <v>45839</v>
       </c>
@@ -23781,7 +24373,7 @@
         <v>66.900000000000006</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31">
       <c r="A85" s="10">
         <v>45870</v>
       </c>
@@ -23822,8 +24414,62 @@
       <c r="M85" s="16">
         <v>71.900000000000006</v>
       </c>
+      <c r="N85" s="16">
+        <v>64</v>
+      </c>
+      <c r="O85" s="16">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="P85" s="16">
+        <v>72.8</v>
+      </c>
+      <c r="Q85" s="16">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="R85" s="16">
+        <v>61.9</v>
+      </c>
+      <c r="S85" s="16">
+        <v>60.7</v>
+      </c>
+      <c r="T85" s="16">
+        <v>48.5</v>
+      </c>
+      <c r="U85" s="16">
+        <v>46.4</v>
+      </c>
+      <c r="V85" s="16">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="W85" s="16">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="X85" s="16">
+        <v>65.3</v>
+      </c>
+      <c r="Y85" s="16">
+        <v>63.5</v>
+      </c>
+      <c r="Z85" s="16">
+        <v>46.8</v>
+      </c>
+      <c r="AA85" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="AB85" s="16">
+        <v>77.5</v>
+      </c>
+      <c r="AC85" s="16">
+        <v>85.2</v>
+      </c>
+      <c r="AD85" s="16">
+        <v>53.3</v>
+      </c>
+      <c r="AE85" s="16">
+        <v>57.1</v>
+      </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31">
       <c r="A86" s="10">
         <v>45901</v>
       </c>
@@ -23864,8 +24510,62 @@
       <c r="M86" s="16">
         <v>66.7</v>
       </c>
+      <c r="N86" s="16">
+        <v>62.8</v>
+      </c>
+      <c r="O86" s="16">
+        <v>55.3</v>
+      </c>
+      <c r="P86" s="16">
+        <v>68.8</v>
+      </c>
+      <c r="Q86" s="16">
+        <v>62.5</v>
+      </c>
+      <c r="R86" s="16">
+        <v>62.3</v>
+      </c>
+      <c r="S86" s="16">
+        <v>50</v>
+      </c>
+      <c r="T86" s="16">
+        <v>50.7</v>
+      </c>
+      <c r="U86" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="V86" s="16">
+        <v>69.8</v>
+      </c>
+      <c r="W86" s="16">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="X86" s="16">
+        <v>61.3</v>
+      </c>
+      <c r="Y86" s="16">
+        <v>52.8</v>
+      </c>
+      <c r="Z86" s="16">
+        <v>47.6</v>
+      </c>
+      <c r="AA86" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="AB86" s="16">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="AC86" s="16">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="AD86" s="16">
+        <v>60.7</v>
+      </c>
+      <c r="AE86" s="16">
+        <v>47.2</v>
+      </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31">
       <c r="A87" s="10">
         <v>45931</v>
       </c>
@@ -23906,8 +24606,62 @@
       <c r="M87" s="16">
         <v>79.7</v>
       </c>
+      <c r="N87" s="16">
+        <v>64.5</v>
+      </c>
+      <c r="O87" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="P87" s="16">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="Q87" s="16">
+        <v>76.3</v>
+      </c>
+      <c r="R87" s="16">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="S87" s="16">
+        <v>66.3</v>
+      </c>
+      <c r="T87" s="16">
+        <v>37</v>
+      </c>
+      <c r="U87" s="16">
+        <v>48.8</v>
+      </c>
+      <c r="V87" s="16">
+        <v>72</v>
+      </c>
+      <c r="W87" s="16">
+        <v>72.2</v>
+      </c>
+      <c r="X87" s="16">
+        <v>71.2</v>
+      </c>
+      <c r="Y87" s="16">
+        <v>67.5</v>
+      </c>
+      <c r="Z87" s="16">
+        <v>46.6</v>
+      </c>
+      <c r="AA87" s="16">
+        <v>59</v>
+      </c>
+      <c r="AB87" s="16">
+        <v>75</v>
+      </c>
+      <c r="AC87" s="16">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="AD87" s="16">
+        <v>51.7</v>
+      </c>
+      <c r="AE87" s="16">
+        <v>40.200000000000003</v>
+      </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31">
       <c r="A88" s="10">
         <v>45962</v>
       </c>
@@ -23948,8 +24702,62 @@
       <c r="M88" s="16">
         <v>78.400000000000006</v>
       </c>
+      <c r="N88" s="16">
+        <v>65</v>
+      </c>
+      <c r="O88" s="16">
+        <v>58</v>
+      </c>
+      <c r="P88" s="16">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="16">
+        <v>73.5</v>
+      </c>
+      <c r="R88" s="16">
+        <v>70</v>
+      </c>
+      <c r="S88" s="16">
+        <v>55.9</v>
+      </c>
+      <c r="T88" s="16">
+        <v>44</v>
+      </c>
+      <c r="U88" s="16">
+        <v>55.9</v>
+      </c>
+      <c r="V88" s="16">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="W88" s="16">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="X88" s="16">
+        <v>60.5</v>
+      </c>
+      <c r="Y88" s="16">
+        <v>61.1</v>
+      </c>
+      <c r="Z88" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="AA88" s="16">
+        <v>58.3</v>
+      </c>
+      <c r="AB88" s="16">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AC88" s="16">
+        <v>63.2</v>
+      </c>
+      <c r="AD88" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="AE88" s="16">
+        <v>57.9</v>
+      </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31">
       <c r="A89" s="10">
         <v>45992</v>
       </c>
@@ -23990,8 +24798,62 @@
       <c r="M89" s="16">
         <v>76.8</v>
       </c>
+      <c r="N89" s="16">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="O89" s="16">
+        <v>57.8</v>
+      </c>
+      <c r="P89" s="16">
+        <v>80.8</v>
+      </c>
+      <c r="Q89" s="16">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="R89" s="16">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="S89" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="T89" s="16">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="U89" s="16">
+        <v>52.4</v>
+      </c>
+      <c r="V89" s="16">
+        <v>76.8</v>
+      </c>
+      <c r="W89" s="16">
+        <v>69</v>
+      </c>
+      <c r="X89" s="16">
+        <v>68.8</v>
+      </c>
+      <c r="Y89" s="16">
+        <v>57.1</v>
+      </c>
+      <c r="Z89" s="16">
+        <v>52.7</v>
+      </c>
+      <c r="AA89" s="16">
+        <v>64.3</v>
+      </c>
+      <c r="AB89" s="16">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="AC89" s="16">
+        <v>73.8</v>
+      </c>
+      <c r="AD89" s="16">
+        <v>63</v>
+      </c>
+      <c r="AE89" s="16">
+        <v>50</v>
+      </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31">
       <c r="A90" s="10">
         <v>46023</v>
       </c>
@@ -24032,8 +24894,62 @@
       <c r="M90" s="16">
         <v>79.5</v>
       </c>
+      <c r="N90" s="16">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="O90" s="16">
+        <v>59.1</v>
+      </c>
+      <c r="P90" s="16">
+        <v>81</v>
+      </c>
+      <c r="Q90" s="16">
+        <v>75.8</v>
+      </c>
+      <c r="R90" s="16">
+        <v>73.8</v>
+      </c>
+      <c r="S90" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="T90" s="16">
+        <v>42.4</v>
+      </c>
+      <c r="U90" s="16">
+        <v>42.2</v>
+      </c>
+      <c r="V90" s="16">
+        <v>77.5</v>
+      </c>
+      <c r="W90" s="16">
+        <v>68.2</v>
+      </c>
+      <c r="X90" s="16">
+        <v>63.8</v>
+      </c>
+      <c r="Y90" s="16">
+        <v>59.1</v>
+      </c>
+      <c r="Z90" s="16">
+        <v>50</v>
+      </c>
+      <c r="AA90" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="AB90" s="16">
+        <v>75.8</v>
+      </c>
+      <c r="AC90" s="16">
+        <v>71.2</v>
+      </c>
+      <c r="AD90" s="16">
+        <v>63.2</v>
+      </c>
+      <c r="AE90" s="16">
+        <v>56.1</v>
+      </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31">
       <c r="A91" s="10">
         <v>46054</v>
       </c>
@@ -24074,8 +24990,62 @@
       <c r="M91" s="16">
         <v>80.3</v>
       </c>
+      <c r="N91" s="16">
+        <v>63.3</v>
+      </c>
+      <c r="O91" s="16">
+        <v>62.5</v>
+      </c>
+      <c r="P91" s="16">
+        <v>81.2</v>
+      </c>
+      <c r="Q91" s="16">
+        <v>79</v>
+      </c>
+      <c r="R91" s="16">
+        <v>75.7</v>
+      </c>
+      <c r="S91" s="16">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="T91" s="16">
+        <v>46.7</v>
+      </c>
+      <c r="U91" s="16">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="V91" s="16">
+        <v>70.2</v>
+      </c>
+      <c r="W91" s="16">
+        <v>68.3</v>
+      </c>
+      <c r="X91" s="16">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="Y91" s="16">
+        <v>68.3</v>
+      </c>
+      <c r="Z91" s="16">
+        <v>51.6</v>
+      </c>
+      <c r="AA91" s="16">
+        <v>51.7</v>
+      </c>
+      <c r="AB91" s="16">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="AC91" s="16">
+        <v>73.3</v>
+      </c>
+      <c r="AD91" s="16">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="AE91" s="16">
+        <v>55</v>
+      </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31">
       <c r="A92" s="10">
         <v>46082</v>
       </c>
@@ -24116,8 +25086,62 @@
       <c r="M92" s="16">
         <v>93</v>
       </c>
+      <c r="N92" s="16">
+        <v>64.8</v>
+      </c>
+      <c r="O92" s="16">
+        <v>61.5</v>
+      </c>
+      <c r="P92" s="16">
+        <v>93.4</v>
+      </c>
+      <c r="Q92" s="16">
+        <v>91.7</v>
+      </c>
+      <c r="R92" s="16">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="S92" s="16">
+        <v>62.5</v>
+      </c>
+      <c r="T92" s="16">
+        <v>33.1</v>
+      </c>
+      <c r="U92" s="16">
+        <v>37.5</v>
+      </c>
+      <c r="V92" s="16">
+        <v>77</v>
+      </c>
+      <c r="W92" s="16">
+        <v>65.2</v>
+      </c>
+      <c r="X92" s="16">
+        <v>63.5</v>
+      </c>
+      <c r="Y92" s="16">
+        <v>68.8</v>
+      </c>
+      <c r="Z92" s="16">
+        <v>54</v>
+      </c>
+      <c r="AA92" s="16">
+        <v>58.7</v>
+      </c>
+      <c r="AB92" s="16">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="AC92" s="16">
+        <v>66.7</v>
+      </c>
+      <c r="AD92" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="AE92" s="16">
+        <v>60.4</v>
+      </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31">
       <c r="A93" s="10">
         <v>46113</v>
       </c>
@@ -24158,8 +25182,62 @@
       <c r="M93" s="16">
         <v>93.9</v>
       </c>
+      <c r="N93" s="16">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="O93" s="16">
+        <v>66.5</v>
+      </c>
+      <c r="P93" s="16">
+        <v>94.9</v>
+      </c>
+      <c r="Q93" s="16">
+        <v>91.9</v>
+      </c>
+      <c r="R93" s="16">
+        <v>78</v>
+      </c>
+      <c r="S93" s="16">
+        <v>66.7</v>
+      </c>
+      <c r="T93" s="16">
+        <v>31.6</v>
+      </c>
+      <c r="U93" s="16">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="V93" s="16">
+        <v>83.3</v>
+      </c>
+      <c r="W93" s="16">
+        <v>78.3</v>
+      </c>
+      <c r="X93" s="16">
+        <v>76.3</v>
+      </c>
+      <c r="Y93" s="16">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="Z93" s="16">
+        <v>50.9</v>
+      </c>
+      <c r="AA93" s="16">
+        <v>50</v>
+      </c>
+      <c r="AB93" s="16">
+        <v>78.7</v>
+      </c>
+      <c r="AC93" s="16">
+        <v>80</v>
+      </c>
+      <c r="AD93" s="16">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="AE93" s="16">
+        <v>60</v>
+      </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31">
       <c r="A94" s="10">
         <v>46143</v>
       </c>
@@ -24200,8 +25278,62 @@
       <c r="M94" s="16">
         <v>91.4</v>
       </c>
+      <c r="N94" s="16">
+        <v>66</v>
+      </c>
+      <c r="O94" s="16">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="P94" s="16">
+        <v>92.5</v>
+      </c>
+      <c r="Q94" s="16">
+        <v>88.7</v>
+      </c>
+      <c r="R94" s="16">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="S94" s="16">
+        <v>71</v>
+      </c>
+      <c r="T94" s="16">
+        <v>34.1</v>
+      </c>
+      <c r="U94" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="V94" s="16">
+        <v>86.1</v>
+      </c>
+      <c r="W94" s="16">
+        <v>71.7</v>
+      </c>
+      <c r="X94" s="16">
+        <v>69.7</v>
+      </c>
+      <c r="Y94" s="16">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="Z94" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="AA94" s="16">
+        <v>59.4</v>
+      </c>
+      <c r="AB94" s="16">
+        <v>84.7</v>
+      </c>
+      <c r="AC94" s="16">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="AD94" s="16">
+        <v>50</v>
+      </c>
+      <c r="AE94" s="16">
+        <v>68.8</v>
+      </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31">
       <c r="A95" s="10">
         <v>46174</v>
       </c>
@@ -24242,8 +25374,62 @@
       <c r="M95" s="16">
         <v>87</v>
       </c>
+      <c r="N95" s="16">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="O95" s="16">
+        <v>71.7</v>
+      </c>
+      <c r="P95" s="16">
+        <v>83.3</v>
+      </c>
+      <c r="Q95" s="16">
+        <v>89.6</v>
+      </c>
+      <c r="R95" s="16">
+        <v>66.7</v>
+      </c>
+      <c r="S95" s="16">
+        <v>82.7</v>
+      </c>
+      <c r="T95" s="16">
+        <v>42.3</v>
+      </c>
+      <c r="U95" s="16">
+        <v>42.5</v>
+      </c>
+      <c r="V95" s="16">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="W95" s="16">
+        <v>75.5</v>
+      </c>
+      <c r="X95" s="16">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="Y95" s="16">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Z95" s="16">
+        <v>48.5</v>
+      </c>
+      <c r="AA95" s="16">
+        <v>50</v>
+      </c>
+      <c r="AB95" s="16">
+        <v>75.8</v>
+      </c>
+      <c r="AC95" s="16">
+        <v>77.8</v>
+      </c>
+      <c r="AD95" s="16">
+        <v>60.3</v>
+      </c>
+      <c r="AE95" s="16">
+        <v>73.3</v>
+      </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31">
       <c r="A96" s="10">
         <v>46204</v>
       </c>
@@ -24348,12 +25534,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -24369,7 +25555,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
@@ -24389,7 +25575,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>
